--- a/output/reports/20260707_欠席分析報告書.xlsx
+++ b/output/reports/20260707_欠席分析報告書.xlsx
@@ -1627,7 +1627,7 @@
           <t>【子供001】
 平均欠席日数は約1.3日と予測された。約5か月後に安定基準へ到達すると予測された。
 【子供002】
-平均欠席日数は約1.8日と予測された。約9か月後に安定基準へ到達すると予測された。</t>
+平均欠席日数は約1.9日と予測された。約9か月後に安定基準へ到達すると予測された。</t>
         </is>
       </c>
       <c r="C37" s="34" t="n"/>
@@ -1743,7 +1743,7 @@
           <t>【子供001】
 平均欠席日数は約1.3日と予測された。約5か月後に安定が見込まれるため、それまでは健康観察と、家庭と保育園・学校との情報共有を継続することが望ましい。
 【子供002】
-平均欠席日数は約1.8日と予測された。約9か月後に安定が見込まれるため、それまでは健康観察と、家庭と保育園・学校との情報共有を継続することが望ましい。</t>
+平均欠席日数は約1.9日と予測された。約9か月後に安定が見込まれるため、それまでは健康観察と、家庭と保育園・学校との情報共有を継続することが望ましい。</t>
         </is>
       </c>
       <c r="C44" s="34" t="n"/>
@@ -2279,7 +2279,7 @@
           <t>【子供001】
 平均欠席日数は約1.3日と予測された。約5か月後に安定が見込まれるため、それまでは健康観察と、家庭と保育園・学校との情報共有を継続することが望ましい。
 【子供002】
-平均欠席日数は約1.8日と予測された。約9か月後に安定が見込まれるため、それまでは健康観察と、家庭と保育園・学校との情報共有を継続することが望ましい。</t>
+平均欠席日数は約1.9日と予測された。約9か月後に安定が見込まれるため、それまでは健康観察と、家庭と保育園・学校との情報共有を継続することが望ましい。</t>
         </is>
       </c>
       <c r="C39" s="34" t="n"/>
